--- a/test/Gprobs_SACOBRA_Py.xlsx
+++ b/test/Gprobs_SACOBRA_Py.xlsx
@@ -5,19 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WUTemp\FH-MassenDaten\svnMonrep\trunk\src\optimizer\COBRA\Myruns\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wolfgang\Documents\GitHub\SACOBRA_Py\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FE37EF-0630-4278-B380-DEB0300B7CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088C2933-9DE7-4E1A-9C80-18C65DE367B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="12216" activeTab="4" xr2:uid="{B1157DA3-90B6-47F1-BD95-BDFAEFD238E4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{B1157DA3-90B6-47F1-BD95-BDFAEFD238E4}"/>
   </bookViews>
   <sheets>
     <sheet name="R" sheetId="2" r:id="rId1"/>
     <sheet name="Python, NONE" sheetId="1" r:id="rId2"/>
     <sheet name="Python, XNEW" sheetId="4" r:id="rId3"/>
     <sheet name="Python, MIDPTS" sheetId="3" r:id="rId4"/>
-    <sheet name="gaussian, MIDPTS" sheetId="6" r:id="rId5"/>
+    <sheet name="Python, MIDPTS+repair" sheetId="7" r:id="rId5"/>
+    <sheet name="gaussian, MIDPTS" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="60">
   <si>
     <t>d</t>
   </si>
@@ -207,12 +208,30 @@
   <si>
     <t>ISA.onlinePLOG = O_LOGIC.MIDPTS, RBF.kernel="gaussian", W_RULE.ONE</t>
   </si>
+  <si>
+    <t>ISA.onlinePLOG = O_LOGIC.MIDPTS, RBF.kernel="cubic", repair with q=10, eps2=0</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+  <si>
+    <t>maxViol</t>
+  </si>
+  <si>
+    <t>n_repair</t>
+  </si>
+  <si>
+    <t>n_rep_suc</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,8 +255,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -277,6 +304,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -528,6 +561,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -536,11 +573,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFCCCC"/>
       <color rgb="FFFFFF99"/>
       <color rgb="FFCCECFF"/>
       <color rgb="FFCCFFCC"/>
       <color rgb="FFFF9999"/>
-      <color rgb="FFFFCCCC"/>
       <color rgb="FFFFFFCC"/>
       <color rgb="FFFFCCFF"/>
     </mruColors>
@@ -4321,20 +4358,31 @@
       </c>
     </row>
     <row r="8" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C8" s="7"/>
-      <c r="D8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="7">
-        <v>13</v>
-      </c>
-      <c r="F8" s="8">
-        <v>500</v>
-      </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="12"/>
+      <c r="C8" s="95" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="96" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="95">
+        <v>2</v>
+      </c>
+      <c r="F8" s="96">
+        <v>500</v>
+      </c>
+      <c r="G8" s="97">
+        <v>900.55052499999999</v>
+      </c>
+      <c r="H8" s="98">
+        <v>2.7726360000000002E-3</v>
+      </c>
+      <c r="I8" s="57">
+        <v>7.9317700000000005E-2</v>
+      </c>
+      <c r="J8" s="50"/>
+      <c r="K8" t="s">
+        <v>32</v>
+      </c>
       <c r="M8" t="s">
         <v>10</v>
       </c>
@@ -4361,31 +4409,28 @@
       </c>
     </row>
     <row r="9" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C9" s="95" t="s">
+      <c r="C9" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="96" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="95">
-        <v>2</v>
-      </c>
-      <c r="F9" s="96">
-        <v>500</v>
-      </c>
-      <c r="G9" s="97">
-        <v>900.55052499999999</v>
-      </c>
-      <c r="H9" s="98">
-        <v>2.7726360000000002E-3</v>
+      <c r="D9" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="26">
+        <v>5</v>
+      </c>
+      <c r="F9" s="27">
+        <v>500</v>
+      </c>
+      <c r="G9" s="28">
+        <v>2109.6086949999999</v>
+      </c>
+      <c r="H9" s="29">
+        <v>0.2440533</v>
       </c>
       <c r="I9" s="57">
-        <v>7.9317700000000005E-2</v>
-      </c>
-      <c r="J9" s="50"/>
-      <c r="K9" t="s">
-        <v>32</v>
-      </c>
+        <v>9.6267580000000005E-2</v>
+      </c>
+      <c r="J9" s="30"/>
       <c r="O9">
         <v>10</v>
       </c>
@@ -4406,20 +4451,28 @@
       </c>
     </row>
     <row r="10" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C10" s="51"/>
-      <c r="D10" s="52" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="51">
-        <v>2</v>
-      </c>
-      <c r="F10" s="52">
-        <v>500</v>
-      </c>
-      <c r="G10" s="53"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="55"/>
+      <c r="C10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="7">
+        <v>7</v>
+      </c>
+      <c r="F10" s="8">
+        <v>500</v>
+      </c>
+      <c r="G10" s="23">
+        <v>3641.345065</v>
+      </c>
+      <c r="H10" s="11">
+        <v>2.2948310000000002E-13</v>
+      </c>
+      <c r="I10" s="57">
+        <v>1.7215410000000001E-10</v>
+      </c>
+      <c r="J10" s="12"/>
       <c r="M10" t="s">
         <v>11</v>
       </c>
@@ -4446,28 +4499,31 @@
       </c>
     </row>
     <row r="11" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C11" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="26">
-        <v>5</v>
-      </c>
-      <c r="F11" s="27">
-        <v>500</v>
-      </c>
-      <c r="G11" s="28">
-        <v>2109.6086949999999</v>
-      </c>
-      <c r="H11" s="29">
-        <v>0.2440533</v>
-      </c>
-      <c r="I11" s="57">
-        <v>9.6267580000000005E-2</v>
-      </c>
-      <c r="J11" s="30"/>
+      <c r="C11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="7">
+        <v>10</v>
+      </c>
+      <c r="F11" s="8">
+        <v>500</v>
+      </c>
+      <c r="G11" s="23">
+        <v>4666.7810250000002</v>
+      </c>
+      <c r="H11" s="11">
+        <v>2.7904900000000002E-12</v>
+      </c>
+      <c r="I11" s="99">
+        <v>0.16356280000000001</v>
+      </c>
+      <c r="J11" s="12"/>
+      <c r="K11" t="s">
+        <v>31</v>
+      </c>
       <c r="M11" t="s">
         <v>12</v>
       </c>
@@ -4494,20 +4550,28 @@
       </c>
     </row>
     <row r="12" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C12" s="31"/>
-      <c r="D12" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="31">
+      <c r="C12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="5">
         <v>5</v>
       </c>
-      <c r="F12" s="32">
-        <v>500</v>
-      </c>
-      <c r="G12" s="33"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="35"/>
+      <c r="F12" s="2">
+        <v>500</v>
+      </c>
+      <c r="G12" s="24">
+        <v>1029.42596</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1.6916599999999999E-10</v>
+      </c>
+      <c r="I12" s="57">
+        <v>2.192497E-10</v>
+      </c>
+      <c r="J12" s="13"/>
       <c r="M12" t="s">
         <v>13</v>
       </c>
@@ -4534,28 +4598,28 @@
       </c>
     </row>
     <row r="13" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="7">
-        <v>7</v>
-      </c>
-      <c r="F13" s="8">
-        <v>500</v>
-      </c>
-      <c r="G13" s="23">
-        <v>3641.345065</v>
-      </c>
-      <c r="H13" s="11">
-        <v>2.2948310000000002E-13</v>
+      <c r="C13" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="41">
+        <v>4</v>
+      </c>
+      <c r="F13" s="42">
+        <v>500</v>
+      </c>
+      <c r="G13" s="43">
+        <v>1889.6052999999999</v>
+      </c>
+      <c r="H13" s="44">
+        <v>-2.7485509999999999E-4</v>
       </c>
       <c r="I13" s="57">
-        <v>1.7215410000000001E-10</v>
-      </c>
-      <c r="J13" s="12"/>
+        <v>2.9612330000000002E-4</v>
+      </c>
+      <c r="J13" s="45"/>
       <c r="M13" t="s">
         <v>14</v>
       </c>
@@ -4582,20 +4646,28 @@
       </c>
     </row>
     <row r="14" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C14" s="9"/>
-      <c r="D14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="9">
-        <v>7</v>
-      </c>
-      <c r="F14" s="1">
-        <v>500</v>
-      </c>
-      <c r="G14" s="25"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="14"/>
+      <c r="C14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="5">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2">
+        <v>500</v>
+      </c>
+      <c r="G14" s="24">
+        <v>1060.36654</v>
+      </c>
+      <c r="H14" s="3">
+        <v>4.3817540000000001E-7</v>
+      </c>
+      <c r="I14" s="57">
+        <v>1.5580219999999999E-7</v>
+      </c>
+      <c r="J14" s="13"/>
       <c r="M14" t="s">
         <v>15</v>
       </c>
@@ -4623,7 +4695,7 @@
     </row>
     <row r="15" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C15" s="7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>7</v>
@@ -4635,18 +4707,15 @@
         <v>500</v>
       </c>
       <c r="G15" s="23">
-        <v>4666.7810250000002</v>
+        <v>2650.098735</v>
       </c>
       <c r="H15" s="11">
-        <v>2.7904900000000002E-12</v>
-      </c>
-      <c r="I15" s="99">
-        <v>0.16356280000000001</v>
+        <v>-3.0554940000000001E-10</v>
+      </c>
+      <c r="I15" s="57">
+        <v>5.8148689999999997E-10</v>
       </c>
       <c r="J15" s="12"/>
-      <c r="K15" t="s">
-        <v>31</v>
-      </c>
       <c r="M15" t="s">
         <v>16</v>
       </c>
@@ -4673,20 +4742,28 @@
       </c>
     </row>
     <row r="16" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C16" s="9"/>
-      <c r="D16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="9">
-        <v>10</v>
-      </c>
-      <c r="F16" s="1">
-        <v>500</v>
-      </c>
-      <c r="G16" s="25"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="14"/>
+      <c r="C16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="5">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2">
+        <v>500</v>
+      </c>
+      <c r="G16" s="24">
+        <v>734.27422999999999</v>
+      </c>
+      <c r="H16" s="3">
+        <v>5.1028829999999999E-12</v>
+      </c>
+      <c r="I16" s="57">
+        <v>1.256475E-10</v>
+      </c>
+      <c r="J16" s="13"/>
       <c r="M16" t="s">
         <v>17</v>
       </c>
@@ -4713,22 +4790,28 @@
       </c>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C17" s="82" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="78" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="77">
-        <v>10</v>
-      </c>
-      <c r="F17" s="78"/>
-      <c r="G17" s="79"/>
-      <c r="H17" s="80"/>
-      <c r="I17" s="79" t="s">
-        <v>29</v>
-      </c>
-      <c r="J17" s="81"/>
+      <c r="C17" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="36">
+        <v>7</v>
+      </c>
+      <c r="F17" s="37">
+        <v>500</v>
+      </c>
+      <c r="G17" s="38">
+        <v>1739.4273499999999</v>
+      </c>
+      <c r="H17" s="39">
+        <v>0.13670750000000001</v>
+      </c>
+      <c r="I17" s="57">
+        <v>103.2727</v>
+      </c>
+      <c r="J17" s="40"/>
       <c r="M17" t="s">
         <v>18</v>
       </c>
@@ -4756,25 +4839,25 @@
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C18" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E18" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F18" s="2">
         <v>500</v>
       </c>
       <c r="G18" s="24">
-        <v>1029.42596</v>
+        <v>1551.05664</v>
       </c>
       <c r="H18" s="3">
-        <v>1.6916599999999999E-10</v>
+        <v>-1.276783E-6</v>
       </c>
       <c r="I18" s="57">
-        <v>2.192497E-10</v>
+        <v>5.1257919999999995E-10</v>
       </c>
       <c r="J18" s="13"/>
       <c r="M18" t="s">
@@ -4803,20 +4886,28 @@
       </c>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C19" s="9"/>
-      <c r="D19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="9">
-        <v>5</v>
-      </c>
-      <c r="F19" s="1">
-        <v>500</v>
-      </c>
-      <c r="G19" s="25"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="14"/>
+      <c r="C19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2</v>
+      </c>
+      <c r="F19" s="8">
+        <v>500</v>
+      </c>
+      <c r="G19" s="23">
+        <v>1708.0123349999999</v>
+      </c>
+      <c r="H19" s="11">
+        <v>-1.9523270000000001E-13</v>
+      </c>
+      <c r="I19" s="57">
+        <v>6.2885620000000004E-13</v>
+      </c>
+      <c r="J19" s="12"/>
       <c r="M19" t="s">
         <v>20</v>
       </c>
@@ -4843,44 +4934,52 @@
       </c>
     </row>
     <row r="20" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C20" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="41">
-        <v>4</v>
-      </c>
-      <c r="F20" s="42">
-        <v>500</v>
-      </c>
-      <c r="G20" s="43">
-        <v>1889.6052999999999</v>
-      </c>
-      <c r="H20" s="44">
-        <v>-2.7485509999999999E-4</v>
+      <c r="C20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="5">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2">
+        <v>500</v>
+      </c>
+      <c r="G20" s="24">
+        <v>804.55390999999997</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1.5876189999999999E-14</v>
       </c>
       <c r="I20" s="57">
-        <v>2.9612330000000002E-4</v>
-      </c>
-      <c r="J20" s="45"/>
+        <v>4.28613E-3</v>
+      </c>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C21" s="61"/>
-      <c r="D21" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="61">
-        <v>4</v>
-      </c>
-      <c r="F21" s="62">
-        <v>500</v>
-      </c>
-      <c r="G21" s="63"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="63"/>
-      <c r="J21" s="64"/>
+      <c r="C21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="7">
+        <v>5</v>
+      </c>
+      <c r="F21" s="8">
+        <v>500</v>
+      </c>
+      <c r="G21" s="23">
+        <v>2255.6287849999999</v>
+      </c>
+      <c r="H21" s="11">
+        <v>7.061261E-9</v>
+      </c>
+      <c r="I21" s="57">
+        <v>4.2607779999999996E-9</v>
+      </c>
+      <c r="J21" s="12"/>
       <c r="M21" t="s">
         <v>33</v>
       </c>
@@ -4904,28 +5003,6 @@
       </c>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C22" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="5">
-        <v>2</v>
-      </c>
-      <c r="F22" s="2">
-        <v>500</v>
-      </c>
-      <c r="G22" s="24">
-        <v>1060.36654</v>
-      </c>
-      <c r="H22" s="3">
-        <v>4.3817540000000001E-7</v>
-      </c>
-      <c r="I22" s="57">
-        <v>1.5580219999999999E-7</v>
-      </c>
-      <c r="J22" s="13"/>
       <c r="P22" t="s">
         <v>39</v>
       </c>
@@ -4943,20 +5020,31 @@
       </c>
     </row>
     <row r="23" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C23" s="9"/>
-      <c r="D23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="9">
-        <v>2</v>
-      </c>
-      <c r="F23" s="1">
-        <v>500</v>
-      </c>
-      <c r="G23" s="25"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="14"/>
+      <c r="C23" s="83" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="77">
+        <v>7</v>
+      </c>
+      <c r="F23" s="78">
+        <v>500</v>
+      </c>
+      <c r="G23" s="79">
+        <v>1706.325525</v>
+      </c>
+      <c r="H23" s="80">
+        <v>4.8106590000000001E-10</v>
+      </c>
+      <c r="I23" s="100">
+        <v>1.5764049999999999E-10</v>
+      </c>
+      <c r="J23" s="81"/>
+      <c r="K23" s="79" t="s">
+        <v>29</v>
+      </c>
       <c r="M23" t="s">
         <v>4</v>
       </c>
@@ -4968,28 +5056,6 @@
       </c>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="7">
-        <v>10</v>
-      </c>
-      <c r="F24" s="8">
-        <v>500</v>
-      </c>
-      <c r="G24" s="23">
-        <v>2650.098735</v>
-      </c>
-      <c r="H24" s="11">
-        <v>-3.0554940000000001E-10</v>
-      </c>
-      <c r="I24" s="57">
-        <v>5.8148689999999997E-10</v>
-      </c>
-      <c r="J24" s="12"/>
       <c r="M24" t="s">
         <v>6</v>
       </c>
@@ -5016,20 +5082,6 @@
       </c>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C25" s="7"/>
-      <c r="D25" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="7">
-        <v>10</v>
-      </c>
-      <c r="F25" s="8">
-        <v>500</v>
-      </c>
-      <c r="G25" s="23"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="12"/>
       <c r="M25" t="s">
         <v>9</v>
       </c>
@@ -5056,28 +5108,6 @@
       </c>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="5">
-        <v>2</v>
-      </c>
-      <c r="F26" s="2">
-        <v>500</v>
-      </c>
-      <c r="G26" s="24">
-        <v>734.27422999999999</v>
-      </c>
-      <c r="H26" s="3">
-        <v>5.1028829999999999E-12</v>
-      </c>
-      <c r="I26" s="57">
-        <v>1.256475E-10</v>
-      </c>
-      <c r="J26" s="13"/>
       <c r="O26">
         <v>5</v>
       </c>
@@ -5098,20 +5128,6 @@
       </c>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C27" s="9"/>
-      <c r="D27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="9">
-        <v>2</v>
-      </c>
-      <c r="F27" s="1">
-        <v>500</v>
-      </c>
-      <c r="G27" s="25"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="14"/>
       <c r="M27" t="s">
         <v>10</v>
       </c>
@@ -5138,28 +5154,6 @@
       </c>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C28" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="36">
-        <v>7</v>
-      </c>
-      <c r="F28" s="37">
-        <v>500</v>
-      </c>
-      <c r="G28" s="38">
-        <v>1739.4273499999999</v>
-      </c>
-      <c r="H28" s="39">
-        <v>0.13670750000000001</v>
-      </c>
-      <c r="I28" s="57">
-        <v>103.2727</v>
-      </c>
-      <c r="J28" s="40"/>
       <c r="O28">
         <v>10</v>
       </c>
@@ -5180,20 +5174,6 @@
       </c>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C29" s="84"/>
-      <c r="D29" s="85" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="84">
-        <v>7</v>
-      </c>
-      <c r="F29" s="85">
-        <v>500</v>
-      </c>
-      <c r="G29" s="86"/>
-      <c r="H29" s="87"/>
-      <c r="I29" s="86"/>
-      <c r="J29" s="88"/>
       <c r="M29" t="s">
         <v>11</v>
       </c>
@@ -5220,24 +5200,6 @@
       </c>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C30" s="89" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="90" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="89">
-        <v>7</v>
-      </c>
-      <c r="F30" s="90">
-        <v>800</v>
-      </c>
-      <c r="G30" s="91"/>
-      <c r="H30" s="92"/>
-      <c r="I30" s="91" t="s">
-        <v>30</v>
-      </c>
-      <c r="J30" s="93"/>
       <c r="M30" t="s">
         <v>12</v>
       </c>
@@ -5264,31 +5226,6 @@
       </c>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C31" s="83" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="78" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="77">
-        <v>7</v>
-      </c>
-      <c r="F31" s="78">
-        <v>500</v>
-      </c>
-      <c r="G31" s="79">
-        <v>1706.325525</v>
-      </c>
-      <c r="H31" s="80">
-        <v>4.8106590000000001E-10</v>
-      </c>
-      <c r="I31" s="100">
-        <v>1.5764049999999999E-10</v>
-      </c>
-      <c r="J31" s="81"/>
-      <c r="K31" s="79" t="s">
-        <v>29</v>
-      </c>
       <c r="M31" t="s">
         <v>13</v>
       </c>
@@ -5315,28 +5252,6 @@
       </c>
     </row>
     <row r="32" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C32" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="5">
-        <v>8</v>
-      </c>
-      <c r="F32" s="2">
-        <v>500</v>
-      </c>
-      <c r="G32" s="24">
-        <v>1551.05664</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1.276783E-6</v>
-      </c>
-      <c r="I32" s="57">
-        <v>5.1257919999999995E-10</v>
-      </c>
-      <c r="J32" s="13"/>
       <c r="M32" t="s">
         <v>14</v>
       </c>
@@ -5362,21 +5277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C33" s="9"/>
-      <c r="D33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="9">
-        <v>8</v>
-      </c>
-      <c r="F33" s="1">
-        <v>500</v>
-      </c>
-      <c r="G33" s="25"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="14"/>
+    <row r="33" spans="13:21" x14ac:dyDescent="0.3">
       <c r="M33" t="s">
         <v>15</v>
       </c>
@@ -5402,29 +5303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C34" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E34" s="7">
-        <v>2</v>
-      </c>
-      <c r="F34" s="8">
-        <v>500</v>
-      </c>
-      <c r="G34" s="23">
-        <v>1708.0123349999999</v>
-      </c>
-      <c r="H34" s="11">
-        <v>-1.9523270000000001E-13</v>
-      </c>
-      <c r="I34" s="57">
-        <v>6.2885620000000004E-13</v>
-      </c>
-      <c r="J34" s="12"/>
+    <row r="34" spans="13:21" x14ac:dyDescent="0.3">
       <c r="M34" t="s">
         <v>16</v>
       </c>
@@ -5450,21 +5329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C35" s="7"/>
-      <c r="D35" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="7">
-        <v>2</v>
-      </c>
-      <c r="F35" s="8">
-        <v>500</v>
-      </c>
-      <c r="G35" s="23"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="12"/>
+    <row r="35" spans="13:21" x14ac:dyDescent="0.3">
       <c r="M35" t="s">
         <v>17</v>
       </c>
@@ -5490,29 +5355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C36" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" s="5">
-        <v>3</v>
-      </c>
-      <c r="F36" s="2">
-        <v>500</v>
-      </c>
-      <c r="G36" s="24">
-        <v>804.55390999999997</v>
-      </c>
-      <c r="H36" s="3">
-        <v>1.5876189999999999E-14</v>
-      </c>
-      <c r="I36" s="57">
-        <v>4.28613E-3</v>
-      </c>
-      <c r="J36" s="13"/>
+    <row r="36" spans="13:21" x14ac:dyDescent="0.3">
       <c r="M36" t="s">
         <v>18</v>
       </c>
@@ -5538,21 +5381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C37" s="9"/>
-      <c r="D37" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="9">
-        <v>3</v>
-      </c>
-      <c r="F37" s="1">
-        <v>500</v>
-      </c>
-      <c r="G37" s="25"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="14"/>
+    <row r="37" spans="13:21" x14ac:dyDescent="0.3">
       <c r="M37" t="s">
         <v>19</v>
       </c>
@@ -5578,29 +5407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C38" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="7">
-        <v>5</v>
-      </c>
-      <c r="F38" s="8">
-        <v>500</v>
-      </c>
-      <c r="G38" s="23">
-        <v>2255.6287849999999</v>
-      </c>
-      <c r="H38" s="11">
-        <v>7.061261E-9</v>
-      </c>
-      <c r="I38" s="57">
-        <v>4.2607779999999996E-9</v>
-      </c>
-      <c r="J38" s="12"/>
+    <row r="38" spans="13:21" x14ac:dyDescent="0.3">
       <c r="M38" t="s">
         <v>20</v>
       </c>
@@ -5626,23 +5433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="3:21" x14ac:dyDescent="0.3">
-      <c r="C39" s="9"/>
-      <c r="D39" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="9">
-        <v>5</v>
-      </c>
-      <c r="F39" s="1">
-        <v>500</v>
-      </c>
-      <c r="G39" s="25"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="14"/>
-    </row>
-    <row r="41" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="41" spans="13:21" x14ac:dyDescent="0.3">
       <c r="Q41" t="s">
         <v>1</v>
       </c>
@@ -5653,7 +5444,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="42" spans="13:21" x14ac:dyDescent="0.3">
       <c r="M42" t="s">
         <v>10</v>
       </c>
@@ -5673,7 +5464,7 @@
         <v>0.47947800000000002</v>
       </c>
     </row>
-    <row r="43" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="43" spans="13:21" x14ac:dyDescent="0.3">
       <c r="N43" t="s">
         <v>7</v>
       </c>
@@ -5705,6 +5496,1342 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05860128-DEA6-48A0-B0AA-29915D533CA8}">
+  <dimension ref="C1:V38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" customWidth="1"/>
+    <col min="5" max="5" width="4.77734375" customWidth="1"/>
+    <col min="6" max="6" width="6.88671875" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" customWidth="1"/>
+    <col min="12" max="12" width="3" customWidth="1"/>
+    <col min="15" max="15" width="7.21875" customWidth="1"/>
+    <col min="19" max="19" width="9.5546875" customWidth="1"/>
+    <col min="20" max="20" width="8.88671875" customWidth="1"/>
+    <col min="21" max="21" width="8.21875" customWidth="1"/>
+    <col min="22" max="22" width="8.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:22" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="C1" s="56" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C2" s="94" t="s">
+        <v>55</v>
+      </c>
+      <c r="M2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C3" s="5"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="6"/>
+      <c r="P3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" t="s">
+        <v>2</v>
+      </c>
+      <c r="S3" t="s">
+        <v>56</v>
+      </c>
+      <c r="T3" t="s">
+        <v>57</v>
+      </c>
+      <c r="U3" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="V3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="103" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="104"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="104"/>
+      <c r="M4" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" t="s">
+        <v>5</v>
+      </c>
+      <c r="O4" t="s">
+        <v>0</v>
+      </c>
+      <c r="P4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q4" s="57"/>
+    </row>
+    <row r="5" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C5" s="7"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="19"/>
+      <c r="M5" t="s">
+        <v>6</v>
+      </c>
+      <c r="N5" t="s">
+        <v>7</v>
+      </c>
+      <c r="O5">
+        <v>13</v>
+      </c>
+      <c r="P5">
+        <v>58.5</v>
+      </c>
+      <c r="Q5" s="57">
+        <v>7891.2078700000002</v>
+      </c>
+      <c r="R5" s="57">
+        <v>1.74154E-11</v>
+      </c>
+      <c r="S5" t="s">
+        <v>56</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>82</v>
+      </c>
+      <c r="V5">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C6" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="10"/>
+      <c r="M6" t="s">
+        <v>9</v>
+      </c>
+      <c r="N6" t="s">
+        <v>7</v>
+      </c>
+      <c r="O6">
+        <v>2</v>
+      </c>
+      <c r="P6">
+        <v>58.5</v>
+      </c>
+      <c r="Q6" s="57">
+        <v>2815.039475</v>
+      </c>
+      <c r="R6" s="57">
+        <v>6.3091250000000002E-10</v>
+      </c>
+      <c r="S6" t="s">
+        <v>56</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>75</v>
+      </c>
+      <c r="V6">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="7">
+        <v>13</v>
+      </c>
+      <c r="F7" s="8">
+        <v>500</v>
+      </c>
+      <c r="G7" s="23">
+        <v>7891.2078700000002</v>
+      </c>
+      <c r="H7" s="11">
+        <v>1.74154E-11</v>
+      </c>
+      <c r="I7" s="57">
+        <v>2.5330290000000001E-7</v>
+      </c>
+      <c r="J7" s="12"/>
+      <c r="O7">
+        <v>5</v>
+      </c>
+      <c r="P7">
+        <v>58.5</v>
+      </c>
+      <c r="Q7">
+        <v>2836.3453500000001</v>
+      </c>
+      <c r="R7" s="57">
+        <v>0.26968150000000002</v>
+      </c>
+      <c r="S7" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>6</v>
+      </c>
+      <c r="V7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C8" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="66" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="65">
+        <v>2</v>
+      </c>
+      <c r="F8" s="66">
+        <v>500</v>
+      </c>
+      <c r="G8" s="67">
+        <v>2815.039475</v>
+      </c>
+      <c r="H8" s="68">
+        <v>6.3091250000000002E-10</v>
+      </c>
+      <c r="I8" s="68">
+        <v>4.0802400000000003E-2</v>
+      </c>
+      <c r="J8" s="68"/>
+      <c r="K8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8" t="s">
+        <v>10</v>
+      </c>
+      <c r="N8" t="s">
+        <v>7</v>
+      </c>
+      <c r="O8">
+        <v>7</v>
+      </c>
+      <c r="P8">
+        <v>58.5</v>
+      </c>
+      <c r="Q8" s="57">
+        <v>3122.9629300000001</v>
+      </c>
+      <c r="R8" s="57">
+        <v>1.598721E-13</v>
+      </c>
+      <c r="S8" t="s">
+        <v>56</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C9" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="26">
+        <v>5</v>
+      </c>
+      <c r="F9" s="27">
+        <v>500</v>
+      </c>
+      <c r="G9" s="28">
+        <v>2836.3453500000001</v>
+      </c>
+      <c r="H9" s="29">
+        <v>0.26968150000000002</v>
+      </c>
+      <c r="I9" s="30">
+        <v>6.7369680000000001E-2</v>
+      </c>
+      <c r="J9" s="30"/>
+      <c r="O9">
+        <v>10</v>
+      </c>
+      <c r="P9">
+        <v>58.5</v>
+      </c>
+      <c r="Q9">
+        <v>3717.4360499999998</v>
+      </c>
+      <c r="R9" s="57">
+        <v>1.7590539999999999E-11</v>
+      </c>
+      <c r="S9" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>1.5</v>
+      </c>
+      <c r="V9">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="10" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="7">
+        <v>7</v>
+      </c>
+      <c r="F10" s="8">
+        <v>500</v>
+      </c>
+      <c r="G10" s="23">
+        <v>3122.9629300000001</v>
+      </c>
+      <c r="H10" s="11">
+        <v>1.598721E-13</v>
+      </c>
+      <c r="I10" s="57">
+        <v>2.5357580000000001E-13</v>
+      </c>
+      <c r="J10" s="12"/>
+      <c r="M10" t="s">
+        <v>11</v>
+      </c>
+      <c r="N10" t="s">
+        <v>7</v>
+      </c>
+      <c r="O10">
+        <v>5</v>
+      </c>
+      <c r="P10">
+        <v>58.5</v>
+      </c>
+      <c r="Q10" s="57">
+        <v>1040.9607800000001</v>
+      </c>
+      <c r="R10" s="57">
+        <v>1.78261E-10</v>
+      </c>
+      <c r="S10" t="s">
+        <v>56</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>155.5</v>
+      </c>
+      <c r="V10">
+        <v>155.5</v>
+      </c>
+    </row>
+    <row r="11" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="7">
+        <v>10</v>
+      </c>
+      <c r="F11" s="8">
+        <v>500</v>
+      </c>
+      <c r="G11" s="23">
+        <v>3717.4360499999998</v>
+      </c>
+      <c r="H11" s="11">
+        <v>1.7590539999999999E-11</v>
+      </c>
+      <c r="I11" s="76">
+        <v>3.80472E-10</v>
+      </c>
+      <c r="J11" s="12"/>
+      <c r="M11" t="s">
+        <v>12</v>
+      </c>
+      <c r="N11" t="s">
+        <v>7</v>
+      </c>
+      <c r="O11">
+        <v>4</v>
+      </c>
+      <c r="P11">
+        <v>58.5</v>
+      </c>
+      <c r="Q11" s="57">
+        <v>1369.0917999999999</v>
+      </c>
+      <c r="R11" s="57">
+        <v>-2.7294480000000001E-4</v>
+      </c>
+      <c r="S11" t="s">
+        <v>56</v>
+      </c>
+      <c r="T11">
+        <v>6.3999999999999997E-5</v>
+      </c>
+      <c r="U11">
+        <v>203</v>
+      </c>
+      <c r="V11">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="12" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="5">
+        <v>5</v>
+      </c>
+      <c r="F12" s="2">
+        <v>500</v>
+      </c>
+      <c r="G12" s="24">
+        <v>1040.9607800000001</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1.78261E-10</v>
+      </c>
+      <c r="I12" s="57">
+        <v>1.1862810000000001E-8</v>
+      </c>
+      <c r="J12" s="13"/>
+      <c r="M12" t="s">
+        <v>13</v>
+      </c>
+      <c r="N12" t="s">
+        <v>7</v>
+      </c>
+      <c r="O12">
+        <v>2</v>
+      </c>
+      <c r="P12">
+        <v>58.5</v>
+      </c>
+      <c r="Q12" s="57">
+        <v>891.13852999999995</v>
+      </c>
+      <c r="R12" s="57">
+        <v>1.9433579999999999E-7</v>
+      </c>
+      <c r="S12" t="s">
+        <v>56</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>174</v>
+      </c>
+      <c r="V12">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="7">
+        <v>4</v>
+      </c>
+      <c r="F13" s="8">
+        <v>500</v>
+      </c>
+      <c r="G13" s="23">
+        <v>1369.0917999999999</v>
+      </c>
+      <c r="H13" s="11">
+        <v>-2.7294480000000001E-4</v>
+      </c>
+      <c r="I13" s="57">
+        <v>2.3758779999999999E-4</v>
+      </c>
+      <c r="J13" s="12"/>
+      <c r="M13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N13" t="s">
+        <v>7</v>
+      </c>
+      <c r="O13">
+        <v>10</v>
+      </c>
+      <c r="P13">
+        <v>58.5</v>
+      </c>
+      <c r="Q13" s="57">
+        <v>2226.6069649999999</v>
+      </c>
+      <c r="R13" s="57">
+        <v>-5.8133590000000002E-10</v>
+      </c>
+      <c r="S13" t="s">
+        <v>56</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>122</v>
+      </c>
+      <c r="V13">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="5">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2">
+        <v>500</v>
+      </c>
+      <c r="G14" s="24">
+        <v>891.13852999999995</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1.9433579999999999E-7</v>
+      </c>
+      <c r="I14" s="57">
+        <v>1.096955E-7</v>
+      </c>
+      <c r="J14" s="13"/>
+      <c r="M14" t="s">
+        <v>15</v>
+      </c>
+      <c r="N14" t="s">
+        <v>7</v>
+      </c>
+      <c r="O14">
+        <v>2</v>
+      </c>
+      <c r="P14">
+        <v>58.5</v>
+      </c>
+      <c r="Q14" s="57">
+        <v>850.73871499999996</v>
+      </c>
+      <c r="R14" s="57">
+        <v>2.8334829999999999E-12</v>
+      </c>
+      <c r="S14" t="s">
+        <v>56</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>1.5</v>
+      </c>
+      <c r="V14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="15" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="7">
+        <v>10</v>
+      </c>
+      <c r="F15" s="8">
+        <v>500</v>
+      </c>
+      <c r="G15" s="23">
+        <v>2226.6069649999999</v>
+      </c>
+      <c r="H15" s="11">
+        <v>-5.8133590000000002E-10</v>
+      </c>
+      <c r="I15" s="57">
+        <v>1.2116920000000001E-10</v>
+      </c>
+      <c r="J15" s="12"/>
+      <c r="M15" t="s">
+        <v>16</v>
+      </c>
+      <c r="N15" t="s">
+        <v>7</v>
+      </c>
+      <c r="O15">
+        <v>7</v>
+      </c>
+      <c r="P15">
+        <v>58.5</v>
+      </c>
+      <c r="Q15" s="57">
+        <v>1750.0861649999999</v>
+      </c>
+      <c r="R15" s="57">
+        <v>8.8986449999999995E-2</v>
+      </c>
+      <c r="S15" t="s">
+        <v>56</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>73.5</v>
+      </c>
+      <c r="V15">
+        <v>73.5</v>
+      </c>
+    </row>
+    <row r="16" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="5">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2">
+        <v>500</v>
+      </c>
+      <c r="G16" s="24">
+        <v>850.73871499999996</v>
+      </c>
+      <c r="H16" s="3">
+        <v>2.8334829999999999E-12</v>
+      </c>
+      <c r="I16" s="106">
+        <v>2.1086460000000001E-2</v>
+      </c>
+      <c r="J16" s="13"/>
+      <c r="M16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" t="s">
+        <v>7</v>
+      </c>
+      <c r="O16">
+        <v>8</v>
+      </c>
+      <c r="P16">
+        <v>58.5</v>
+      </c>
+      <c r="Q16" s="57">
+        <v>1907.4086</v>
+      </c>
+      <c r="R16" s="57">
+        <v>-1.2767110000000001E-6</v>
+      </c>
+      <c r="S16" t="s">
+        <v>56</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>87</v>
+      </c>
+      <c r="V16">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C17" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="36">
+        <v>7</v>
+      </c>
+      <c r="F17" s="37">
+        <v>500</v>
+      </c>
+      <c r="G17" s="38">
+        <v>1750.0861649999999</v>
+      </c>
+      <c r="H17" s="68">
+        <v>8.8986449999999995E-2</v>
+      </c>
+      <c r="I17" s="87">
+        <v>1.4292229999999999</v>
+      </c>
+      <c r="J17" s="39"/>
+      <c r="K17" t="s">
+        <v>31</v>
+      </c>
+      <c r="M17" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" t="s">
+        <v>7</v>
+      </c>
+      <c r="O17">
+        <v>2</v>
+      </c>
+      <c r="P17">
+        <v>58.5</v>
+      </c>
+      <c r="Q17" s="57">
+        <v>1691.0621699999999</v>
+      </c>
+      <c r="R17" s="57">
+        <v>-8.6874950000000002E-13</v>
+      </c>
+      <c r="S17" t="s">
+        <v>56</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>3.5</v>
+      </c>
+      <c r="V17">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="5">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2">
+        <v>500</v>
+      </c>
+      <c r="G18" s="24">
+        <v>1907.4086</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-1.2767110000000001E-6</v>
+      </c>
+      <c r="I18" s="57">
+        <v>3.2798369999999998E-10</v>
+      </c>
+      <c r="J18" s="13"/>
+      <c r="M18" t="s">
+        <v>19</v>
+      </c>
+      <c r="N18" t="s">
+        <v>7</v>
+      </c>
+      <c r="O18">
+        <v>3</v>
+      </c>
+      <c r="P18">
+        <v>58.5</v>
+      </c>
+      <c r="Q18">
+        <v>982.06364499999995</v>
+      </c>
+      <c r="R18" s="57">
+        <v>1.4488409999999999E-14</v>
+      </c>
+      <c r="S18" t="s">
+        <v>56</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>6.5</v>
+      </c>
+      <c r="V18">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2</v>
+      </c>
+      <c r="F19" s="8">
+        <v>500</v>
+      </c>
+      <c r="G19" s="23">
+        <v>1691.0621699999999</v>
+      </c>
+      <c r="H19" s="11">
+        <v>-8.6874950000000002E-13</v>
+      </c>
+      <c r="I19" s="108">
+        <v>5.9673439999999998E-12</v>
+      </c>
+      <c r="J19" s="12"/>
+      <c r="M19" t="s">
+        <v>20</v>
+      </c>
+      <c r="N19" t="s">
+        <v>7</v>
+      </c>
+      <c r="O19">
+        <v>5</v>
+      </c>
+      <c r="P19">
+        <v>58.5</v>
+      </c>
+      <c r="Q19">
+        <v>2294.2720899999999</v>
+      </c>
+      <c r="R19" s="57">
+        <v>7.1454430000000002E-9</v>
+      </c>
+      <c r="S19" t="s">
+        <v>56</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>127.5</v>
+      </c>
+      <c r="V19">
+        <v>127.5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="5">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2">
+        <v>500</v>
+      </c>
+      <c r="G20" s="24">
+        <v>982.06364499999995</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1.4488409999999999E-14</v>
+      </c>
+      <c r="I20" s="57">
+        <v>2.717133E-3</v>
+      </c>
+      <c r="J20" s="13"/>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C21" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="9">
+        <v>5</v>
+      </c>
+      <c r="F21" s="1">
+        <v>500</v>
+      </c>
+      <c r="G21" s="25">
+        <v>2294.2720899999999</v>
+      </c>
+      <c r="H21" s="4">
+        <v>7.1454430000000002E-9</v>
+      </c>
+      <c r="I21" s="107">
+        <v>0.1217163</v>
+      </c>
+      <c r="J21" s="14"/>
+      <c r="M21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N21" t="s">
+        <v>41</v>
+      </c>
+      <c r="O21" t="s">
+        <v>35</v>
+      </c>
+      <c r="P21" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>37</v>
+      </c>
+      <c r="R21" t="s">
+        <v>38</v>
+      </c>
+      <c r="S21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="P22" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>57</v>
+      </c>
+      <c r="R22" t="s">
+        <v>58</v>
+      </c>
+      <c r="S22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="M23" t="s">
+        <v>4</v>
+      </c>
+      <c r="N23" t="s">
+        <v>5</v>
+      </c>
+      <c r="O23" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="M24" t="s">
+        <v>6</v>
+      </c>
+      <c r="N24" t="s">
+        <v>7</v>
+      </c>
+      <c r="O24">
+        <v>13</v>
+      </c>
+      <c r="P24" s="57">
+        <v>2.5330290000000001E-7</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24" s="105">
+        <v>7.9302520000000003</v>
+      </c>
+      <c r="S24" s="105">
+        <v>7.9302520000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="M25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N25" t="s">
+        <v>7</v>
+      </c>
+      <c r="O25">
+        <v>2</v>
+      </c>
+      <c r="P25" s="57">
+        <v>4.0802400000000003E-2</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25" s="105">
+        <v>29.848506</v>
+      </c>
+      <c r="S25" s="105">
+        <v>29.848506</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="O26">
+        <v>5</v>
+      </c>
+      <c r="P26" s="57">
+        <v>6.7369680000000001E-2</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26" s="105">
+        <v>13.914021999999999</v>
+      </c>
+      <c r="S26" s="105">
+        <v>13.914021999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="M27" t="s">
+        <v>10</v>
+      </c>
+      <c r="N27" t="s">
+        <v>7</v>
+      </c>
+      <c r="O27">
+        <v>7</v>
+      </c>
+      <c r="P27" s="57">
+        <v>2.5357580000000001E-13</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27" s="105">
+        <v>0</v>
+      </c>
+      <c r="S27" s="105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="O28">
+        <v>10</v>
+      </c>
+      <c r="P28" s="57">
+        <v>3.80472E-10</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28" s="105">
+        <v>1.0801229999999999</v>
+      </c>
+      <c r="S28" s="105">
+        <v>1.0801229999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="M29" t="s">
+        <v>11</v>
+      </c>
+      <c r="N29" t="s">
+        <v>7</v>
+      </c>
+      <c r="O29">
+        <v>5</v>
+      </c>
+      <c r="P29" s="57">
+        <v>1.1862810000000001E-8</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29" s="105">
+        <v>12.667104999999999</v>
+      </c>
+      <c r="S29" s="105">
+        <v>12.667104999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="M30" t="s">
+        <v>12</v>
+      </c>
+      <c r="N30" t="s">
+        <v>7</v>
+      </c>
+      <c r="O30">
+        <v>4</v>
+      </c>
+      <c r="P30" s="57">
+        <v>2.3758779999999999E-4</v>
+      </c>
+      <c r="Q30">
+        <v>3.6999999999999998E-5</v>
+      </c>
+      <c r="R30" s="105">
+        <v>11.698053</v>
+      </c>
+      <c r="S30" s="105">
+        <v>11.698053</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="M31" t="s">
+        <v>13</v>
+      </c>
+      <c r="N31" t="s">
+        <v>7</v>
+      </c>
+      <c r="O31">
+        <v>2</v>
+      </c>
+      <c r="P31" s="57">
+        <v>1.096955E-7</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31" s="105">
+        <v>6.3104849999999999</v>
+      </c>
+      <c r="S31" s="105">
+        <v>6.3104849999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="M32" t="s">
+        <v>14</v>
+      </c>
+      <c r="N32" t="s">
+        <v>7</v>
+      </c>
+      <c r="O32">
+        <v>10</v>
+      </c>
+      <c r="P32" s="57">
+        <v>1.2116920000000001E-10</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32" s="105">
+        <v>9.3547370000000001</v>
+      </c>
+      <c r="S32" s="105">
+        <v>9.3547370000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="13:19" x14ac:dyDescent="0.3">
+      <c r="M33" t="s">
+        <v>15</v>
+      </c>
+      <c r="N33" t="s">
+        <v>7</v>
+      </c>
+      <c r="O33">
+        <v>2</v>
+      </c>
+      <c r="P33" s="57">
+        <v>2.1086460000000001E-2</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33" s="105">
+        <v>5.8013409999999999</v>
+      </c>
+      <c r="S33" s="105">
+        <v>5.8013409999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="13:19" x14ac:dyDescent="0.3">
+      <c r="M34" t="s">
+        <v>16</v>
+      </c>
+      <c r="N34" t="s">
+        <v>7</v>
+      </c>
+      <c r="O34">
+        <v>7</v>
+      </c>
+      <c r="P34" s="57">
+        <v>1.4292229999999999</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34" s="105">
+        <v>10.064238</v>
+      </c>
+      <c r="S34" s="105">
+        <v>10.064238</v>
+      </c>
+    </row>
+    <row r="35" spans="13:19" x14ac:dyDescent="0.3">
+      <c r="M35" t="s">
+        <v>17</v>
+      </c>
+      <c r="N35" t="s">
+        <v>7</v>
+      </c>
+      <c r="O35">
+        <v>8</v>
+      </c>
+      <c r="P35" s="57">
+        <v>3.2798369999999998E-10</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35" s="105">
+        <v>7.2387839999999999</v>
+      </c>
+      <c r="S35" s="105">
+        <v>7.2387839999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="13:19" x14ac:dyDescent="0.3">
+      <c r="M36" t="s">
+        <v>18</v>
+      </c>
+      <c r="N36" t="s">
+        <v>7</v>
+      </c>
+      <c r="O36">
+        <v>2</v>
+      </c>
+      <c r="P36" s="57">
+        <v>5.9673439999999998E-12</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36" s="105">
+        <v>3.910101</v>
+      </c>
+      <c r="S36" s="105">
+        <v>3.910101</v>
+      </c>
+    </row>
+    <row r="37" spans="13:19" x14ac:dyDescent="0.3">
+      <c r="M37" t="s">
+        <v>19</v>
+      </c>
+      <c r="N37" t="s">
+        <v>7</v>
+      </c>
+      <c r="O37">
+        <v>3</v>
+      </c>
+      <c r="P37" s="57">
+        <v>2.717133E-3</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37" s="105">
+        <v>31.415495</v>
+      </c>
+      <c r="S37" s="105">
+        <v>31.415495</v>
+      </c>
+    </row>
+    <row r="38" spans="13:19" x14ac:dyDescent="0.3">
+      <c r="M38" t="s">
+        <v>20</v>
+      </c>
+      <c r="N38" t="s">
+        <v>7</v>
+      </c>
+      <c r="O38">
+        <v>5</v>
+      </c>
+      <c r="P38" s="57">
+        <v>0.1217163</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38" s="105">
+        <v>15.640404</v>
+      </c>
+      <c r="S38" s="105">
+        <v>15.640404</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F8766CB-5C8D-41CD-9F67-76856DA56D72}">
   <dimension ref="C1:T52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
